--- a/artfynd/A 41645-2024 artfynd.xlsx
+++ b/artfynd/A 41645-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56145589</v>
+        <v>56145590</v>
       </c>
       <c r="B2" t="n">
-        <v>99882</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1365</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595213</v>
+        <v>595450</v>
       </c>
       <c r="R2" t="n">
-        <v>7184346</v>
+        <v>7184301</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +760,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56145590</v>
+        <v>56145589</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595450.3522426649</v>
+        <v>595213</v>
       </c>
       <c r="R3" t="n">
-        <v>7184300.952749167</v>
+        <v>7184346</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,19 +854,9 @@
           <t>2015-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,11 +871,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>gransumpskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
